--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,36 +632,32 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -669,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,37 +689,33 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -842,22 +834,22 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -890,12 +882,12 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -945,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -953,7 +945,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -963,7 +955,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1001,12 +993,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1020,7 +1012,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1056,7 +1048,1339 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A00251D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A66775D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1109,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1169,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1187,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1220,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1244,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1492,7 +1540,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1651,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1751,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1714,7 +1762,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1873,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1984,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1992,7 @@
       <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>沪A66775D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1954,7 +2002,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1992,12 +2040,12 @@
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2011,7 +2059,7 @@
       <c r="T14" s="2" t="inlineStr"/>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -2047,7 +2095,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2103,7 @@
       <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A66775D</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2103,12 +2151,12 @@
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2206,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2317,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2277,22 +2325,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2325,12 +2373,12 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2344,7 +2392,7 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2369,7 +2417,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2380,7 +2428,1026 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A00251D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1118,24 +1118,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1346,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1457,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1490,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,17 +1526,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1534,13 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1568,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1601,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1625,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1712,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1736,17 +1764,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1756,13 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1862,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1901,32 +1933,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -1934,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1958,33 +1994,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2123,32 +2163,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -2156,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2180,17 +2224,17 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2200,13 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2234,32 +2282,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2267,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2291,33 +2343,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2543,7 +2599,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2769,7 +2825,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2869,7 +2925,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2941,7 +2997,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2980,7 +3036,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -2995,7 +3051,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3112,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3110,7 +3166,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3227,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3225,7 +3281,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3330,13 +3386,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3344,22 +3404,22 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A00251D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3392,12 +3452,12 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3411,43 +3471,959 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A00251D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>09:05</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z26" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr"/>
-      <c r="AC26" s="2" t="inlineStr">
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2512,32 +2512,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2545,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2569,17 +2573,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2589,12 +2593,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2660,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,7 +2703,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2771,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2886,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2997,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3112,7 +3116,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3227,7 +3231,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3342,7 +3346,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3457,7 +3461,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3572,7 +3576,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3687,7 +3691,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,7 +3806,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,7 +3921,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4139,7 +4143,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4201,22 +4205,22 @@
       <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A66775D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4249,12 +4253,12 @@
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4268,7 +4272,7 @@
       <c r="T33" s="2" t="inlineStr"/>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4303,12 +4307,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4316,22 +4320,22 @@
       <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4364,12 +4368,12 @@
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4383,45 +4387,271 @@
       <c r="T34" s="2" t="inlineStr"/>
       <c r="U34" s="2" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W34" s="2" t="inlineStr">
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X34" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="Z36" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
+      <c r="AA36" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
+      <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="AC34" s="2" t="inlineStr">
+      <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>12/18</t>
         </is>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2631,32 +2631,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2664,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2688,17 +2692,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2708,13 +2712,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2742,32 +2750,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2775,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2799,32 +2811,32 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2890,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,32 +2980,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3001,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3025,17 +3041,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3045,17 +3061,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3155,7 +3171,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3170,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3270,7 +3286,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3285,7 +3301,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3313,32 +3329,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3346,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3370,32 +3390,32 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3461,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3515,7 +3535,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3543,32 +3563,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3576,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3600,37 +3624,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3658,32 +3682,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3691,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3715,37 +3743,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3860,7 +3888,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3949,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,7 +4060,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,7 +4171,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4197,7 +4225,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4286,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4312,7 +4340,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4417,13 +4445,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4516,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4546,22 +4578,22 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4594,12 +4626,12 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4613,47 +4645,737 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>12/18</t>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A00251D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,22 +2009,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3056,22 +3056,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -3801,32 +3801,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3834,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3858,17 +3862,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3878,17 +3882,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3999,7 +4003,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4064,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4099,7 +4103,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4110,7 +4114,7 @@
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -4138,32 +4142,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -4171,7 +4179,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4195,37 +4203,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4294,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4340,7 +4348,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -4368,32 +4376,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4401,7 +4413,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4425,17 +4437,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4445,17 +4457,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -4483,32 +4495,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4516,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4540,37 +4556,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -4598,32 +4614,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4631,7 +4651,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4655,37 +4675,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4766,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4800,7 +4820,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -4828,32 +4848,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4861,7 +4885,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4885,37 +4909,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -4976,7 +5000,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5015,7 +5039,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5030,7 +5054,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5115,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5145,7 +5169,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5230,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5245,7 +5269,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5260,7 +5284,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -5268,22 +5292,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5316,12 +5340,12 @@
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5335,47 +5359,959 @@
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>7/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
+      <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>96.0</t>
         </is>
       </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>7/18</t>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>1/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A56171D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>6/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>2/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>11/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>3/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,22 +2009,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3291,17 +3291,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3639,22 +3639,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4218,22 +4218,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4571,17 +4571,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4624,24 +4624,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -4858,24 +4858,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -5197,32 +5197,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5230,7 +5234,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5254,17 +5258,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5274,17 +5278,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -5312,32 +5316,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -5345,7 +5353,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5369,37 +5377,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -5427,32 +5435,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5460,7 +5472,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5484,37 +5496,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -5542,32 +5554,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5575,7 +5591,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5599,32 +5615,32 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5768,32 +5784,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
@@ -5801,7 +5821,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5825,33 +5845,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5936,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5961,12 +5985,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6051,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6066,7 +6090,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6076,12 +6100,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6166,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6186,17 +6210,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6281,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6311,6 +6335,581 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
+          <t>5/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>90.7</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>8/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>9/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A56171D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>3/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>1/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
           <t>3/19</t>
         </is>
       </c>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3056,22 +3056,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3405,22 +3405,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4924,22 +4924,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5039,22 +5039,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5273,17 +5273,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5564,24 +5564,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -5903,32 +5903,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5936,7 +5940,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5960,37 +5964,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -6018,32 +6022,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6051,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6075,17 +6083,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6095,12 +6103,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6133,32 +6141,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6166,7 +6178,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6190,32 +6202,32 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6248,32 +6260,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6281,7 +6297,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6305,37 +6321,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6412,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6511,7 +6527,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6550,7 +6566,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6560,12 +6576,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6642,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6680,7 +6696,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6757,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6790,7 +6806,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6856,7 +6872,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6900,17 +6916,592 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>3/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>91.2</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>9/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>3/19</t>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>4/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>2/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>11/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3639,22 +3639,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4223,17 +4223,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4571,22 +4571,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4695,17 +4695,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5397,17 +5397,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5511,22 +5511,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5630,22 +5630,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5860,22 +5860,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6103,17 +6103,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -6270,24 +6270,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -6379,32 +6379,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6412,7 +6416,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6436,37 +6440,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -6494,32 +6498,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6527,7 +6535,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6551,17 +6559,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6571,17 +6579,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -6609,32 +6617,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>11:00</t>
@@ -6642,7 +6654,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6666,37 +6678,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -6724,32 +6736,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6757,7 +6773,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6781,37 +6797,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -6839,32 +6855,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6872,7 +6892,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6896,17 +6916,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6916,17 +6936,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -6987,7 +7007,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7041,7 +7061,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7122,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7151,12 +7171,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7237,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7271,7 +7291,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7352,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7376,17 +7396,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7467,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7505,6 +7525,573 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>6/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A56171D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>3/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>2/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,14 +2707,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>90.0</t>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3056,22 +3056,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4223,17 +4223,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4452,14 +4452,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>90.0</t>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq26推进至seq34，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4774,10 +4774,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>五莲路凌河路</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4805,7 +4817,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4885,7 +4897,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4924,22 +4936,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5012,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5044,12 +5056,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5082,12 +5094,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq24推进至seq28，推进4站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -5115,7 +5127,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5123,10 +5135,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>五莲路东陆路</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="inlineStr"/>
-      <c r="T40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq18映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5154,7 +5178,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5169,7 +5193,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5258,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5278,12 +5302,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5353,7 +5377,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5397,17 +5421,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5496,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5591,7 +5615,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5706,7 +5730,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5745,7 +5769,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5940,7 +5964,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5979,22 +6003,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6083,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6098,7 +6122,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6178,7 +6202,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6222,12 +6246,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6297,7 +6321,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6341,12 +6365,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6416,7 +6440,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,7 +6559,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6579,17 +6603,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6797,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,7 +6916,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6931,7 +6955,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6974,32 +6998,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7007,7 +7035,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7031,37 +7059,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -7089,32 +7117,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7122,7 +7154,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7146,17 +7178,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7166,12 +7198,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7204,32 +7236,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7237,7 +7273,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7261,17 +7297,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7281,12 +7317,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7319,32 +7355,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -7352,7 +7392,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7376,17 +7416,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7396,17 +7436,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7507,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7582,7 +7622,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7697,7 +7737,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7755,7 +7795,7 @@
       <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>沪A56171D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -7803,12 +7843,12 @@
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7847,22 +7887,18 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>84.5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr"/>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -7870,22 +7906,22 @@
       <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56171D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -7918,7 +7954,7 @@
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -7937,7 +7973,7 @@
       <c r="T64" s="2" t="inlineStr"/>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
@@ -7962,22 +7998,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -7985,7 +8021,7 @@
       <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -7995,7 +8031,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -8033,12 +8069,12 @@
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8052,43 +8088,963 @@
       <c r="T65" s="2" t="inlineStr"/>
       <c r="U65" s="2" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>2/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>15/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
           <t>15:15</t>
         </is>
       </c>
-      <c r="V65" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W65" s="2" t="inlineStr">
+      <c r="W67" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X65" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y65" s="2" t="inlineStr">
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z65" s="2" t="inlineStr">
+      <c r="Z67" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
+      <c r="AA67" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr"/>
-      <c r="AC65" s="2" t="inlineStr">
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
         <is>
           <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>11/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>13/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>9/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>89.6</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>7/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A00251D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>84.8</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>4/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,18 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,18 +2128,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,17 +2366,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2434,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2549,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2787,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3017,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3071,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3186,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3286,7 +3294,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3366,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3405,7 +3413,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3420,7 +3428,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3520,22 +3528,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3639,22 +3647,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3892,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4103,18 +4111,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4218,22 +4230,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4360,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4532,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4571,17 +4583,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4651,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4766,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4832,7 +4844,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4951,7 +4963,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5051,7 +5063,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5066,7 +5078,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5111,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq24推进至seq28，推进4站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq24推进至seq36，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -5127,7 +5139,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5193,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5297,7 +5309,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5377,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5416,22 +5428,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5535,22 +5547,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5654,17 +5666,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5730,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5769,18 +5781,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6018,7 +6034,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6202,7 +6218,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6241,7 +6257,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6321,7 +6337,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6360,7 +6376,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6375,7 +6391,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -6440,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6479,22 +6495,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6575,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6598,22 +6614,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6836,17 +6852,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6916,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7035,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7089,7 +7105,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7193,7 +7209,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7208,7 +7224,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -7273,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7312,7 +7328,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7365,19 +7381,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7392,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7431,22 +7447,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -7474,32 +7490,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7507,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7531,37 +7551,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -7589,32 +7609,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7622,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7646,37 +7670,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -7704,32 +7728,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7737,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7761,33 +7789,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -7815,32 +7847,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -7848,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7872,33 +7908,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB63" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -8041,32 +8081,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8074,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8098,32 +8142,32 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8156,32 +8200,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8189,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8213,37 +8261,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8352,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8415,7 +8463,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8469,7 +8517,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -8530,7 +8578,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8584,7 +8632,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8693,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8760,7 +8808,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8814,7 +8862,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -8875,7 +8923,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8929,7 +8977,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -8990,7 +9038,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9048,6 +9096,1041 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>1/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>6/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>91.3</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>12/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>13/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>7/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>5/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>9/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>2/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>17/19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4702,22 +4702,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6138,22 +6138,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6971,22 +6971,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8222,12 +8222,12 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9005,32 +9005,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9038,7 +9042,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9062,37 +9066,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9157,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9268,7 +9272,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9322,7 +9326,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -9383,7 +9387,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9498,7 +9502,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9613,7 +9617,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9728,7 +9732,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9782,7 +9786,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -9843,7 +9847,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9958,7 +9962,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10073,7 +10077,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10131,6 +10135,692 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>14/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>9/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>6/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>15/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>89.6</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>8/19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC88"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3294,22 +3294,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3652,17 +3652,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5190,22 +5190,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5309,22 +5309,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,17 +5552,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6257,22 +6257,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6500,17 +6500,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7328,22 +7328,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7566,22 +7566,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7690,17 +7690,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -8890,32 +8890,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>118分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8923,7 +8927,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8947,37 +8951,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9046,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9096,7 +9100,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -9124,32 +9128,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9157,7 +9165,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9181,37 +9189,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9280,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9311,7 +9319,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9326,7 +9334,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -9354,32 +9362,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9387,7 +9399,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9411,37 +9423,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9514,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9541,7 +9553,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9556,7 +9568,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -9584,32 +9596,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9617,7 +9633,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9641,17 +9657,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9661,17 +9677,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9748,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9786,7 +9802,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9863,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9886,7 +9902,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9901,7 +9917,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -9962,7 +9978,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10016,7 +10032,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -10077,7 +10093,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10192,7 +10208,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10246,7 +10262,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -10307,7 +10323,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10418,7 +10434,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10472,7 +10488,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10549,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10587,7 +10603,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10621,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -10648,7 +10664,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10662,7 +10678,7 @@
       <c r="T87" s="2" t="inlineStr"/>
       <c r="U87" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="V87" s="2" t="inlineStr">
@@ -10702,7 +10718,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -10710,22 +10726,22 @@
       <c r="A88" s="2" t="inlineStr"/>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -10758,12 +10774,12 @@
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10777,7 +10793,7 @@
       <c r="T88" s="2" t="inlineStr"/>
       <c r="U88" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="V88" s="2" t="inlineStr">
@@ -10807,15 +10823,705 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>4/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB88" s="2" t="inlineStr">
+      <c r="AB89" s="2" t="inlineStr">
         <is>
           <t>89.6</t>
         </is>
       </c>
-      <c r="AC88" s="2" t="inlineStr">
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>7/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A00251D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>99.7</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>16/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>6/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>95.2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>13/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
         <is>
           <t>8/19</t>
         </is>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>104.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,18 +2481,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>18/19</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2611,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>104.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,17 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3069,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,17 +3183,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3255,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3309,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3428,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3528,22 +3532,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>104.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3770,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3781,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,22 +3889,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4111,22 +4115,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4245,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4364,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4464,22 +4468,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>104.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4588,17 +4592,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4707,17 +4711,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4829,17 +4833,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4909,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4953,17 +4957,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5078,7 +5082,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5190,7 +5194,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5205,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5324,7 +5328,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5443,7 +5447,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5566,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5671,17 +5675,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5781,22 +5785,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5919,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6024,17 +6028,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6143,17 +6147,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6272,7 +6276,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6391,7 +6395,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6514,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6629,7 +6633,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6752,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6857,17 +6861,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6976,17 +6980,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7095,17 +7099,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7224,7 +7228,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7343,7 +7347,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7462,7 +7466,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7566,7 +7570,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7581,7 +7585,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -7700,7 +7704,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7819,7 +7823,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7923,22 +7927,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8057,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8122,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8162,17 +8166,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8276,22 +8280,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>104.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8391,18 +8395,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>18/19</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8502,22 +8510,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8586,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8617,17 +8625,17 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8693,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8732,22 +8740,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>104.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8816,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8852,17 +8860,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8935,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8966,7 +8974,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -8981,7 +8989,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9054,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9090,17 +9098,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9173,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9219,7 +9227,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -9280,7 +9288,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9334,7 +9342,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -9399,7 +9407,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9438,7 +9446,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9453,7 +9461,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9522,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9568,7 +9576,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9695,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -9715,32 +9723,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9748,7 +9760,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9772,37 +9784,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -9863,7 +9875,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9917,7 +9929,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -9945,32 +9957,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9978,7 +9994,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10002,17 +10018,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10022,17 +10038,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -10060,32 +10076,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10093,7 +10113,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10117,37 +10137,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>104.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -10175,32 +10195,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10208,7 +10232,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10232,37 +10256,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -10290,32 +10314,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -10323,7 +10351,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10347,33 +10375,37 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB84" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>18/19</t>
         </is>
       </c>
     </row>
@@ -10401,32 +10433,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10434,7 +10470,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10458,37 +10494,37 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>104.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -10516,32 +10552,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10549,7 +10589,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10573,17 +10613,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10593,17 +10633,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -10631,32 +10671,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10664,7 +10708,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10688,32 +10732,32 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10779,7 +10823,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10833,7 +10877,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -10861,32 +10905,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10894,7 +10942,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10918,17 +10966,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10938,17 +10986,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11057,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11048,7 +11096,7 @@
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
@@ -11063,7 +11111,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -11071,22 +11119,22 @@
       <c r="A91" s="2" t="inlineStr"/>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>18:25</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -11119,12 +11167,12 @@
       <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11173,12 +11221,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -11186,22 +11234,22 @@
       <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>18:25</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11234,12 +11282,12 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11253,7 +11301,7 @@
       <c r="T92" s="2" t="inlineStr"/>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
@@ -11288,12 +11336,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11402,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11393,7 +11441,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11408,7 +11456,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11517,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11523,7 +11571,927 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>5/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>104.7</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>16/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>18/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>14/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>15/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A00251D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>99.7</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>13/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>104.7</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>16/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>95.2</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>11/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC102"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>104.7</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>104.7</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,22 +3532,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>104.7</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4120,17 +4120,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4478,12 +4478,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>104.7</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5072,17 +5072,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5790,17 +5790,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6385,17 +6385,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7218,17 +7218,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7575,17 +7575,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7813,17 +7813,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7932,17 +7932,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8280,22 +8280,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>104.7</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8750,12 +8750,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>104.7</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8865,12 +8865,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9173,7 +9173,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9332,17 +9332,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9566,12 +9566,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9804,17 +9804,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9919,17 +9919,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10048,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10152,22 +10152,22 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>104.7</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10443,24 +10443,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>104.7</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -10790,32 +10790,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10823,7 +10827,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10847,17 +10851,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10867,17 +10871,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -10915,24 +10919,24 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10942,7 +10946,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10991,12 +10995,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -11057,7 +11061,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11172,7 +11176,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11226,7 +11230,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -11254,32 +11258,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11287,7 +11295,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11311,17 +11319,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11331,12 +11339,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11369,32 +11377,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -11402,7 +11414,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11426,17 +11438,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11446,17 +11458,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -11484,32 +11496,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11517,7 +11533,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11541,17 +11557,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11561,17 +11577,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -11599,32 +11615,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11632,7 +11652,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11656,17 +11676,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11676,17 +11696,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -11714,32 +11734,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -11747,7 +11771,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11771,37 +11795,37 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>104.7</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11886,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11977,7 +12001,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12031,7 +12055,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -12092,7 +12116,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12131,7 +12155,7 @@
       </c>
       <c r="Z99" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA99" s="2" t="inlineStr">
@@ -12146,7 +12170,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -12207,7 +12231,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12322,7 +12346,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12361,7 +12385,7 @@
       </c>
       <c r="Z101" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA101" s="2" t="inlineStr">
@@ -12371,12 +12395,12 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>104.7</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -12437,7 +12461,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12481,17 +12505,362 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>92.8</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB102" s="2" t="inlineStr">
-        <is>
-          <t>95.2</t>
-        </is>
-      </c>
-      <c r="AC102" s="2" t="inlineStr">
-        <is>
-          <t>11/19</t>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>100.2</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>14/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>16/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>17/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3894,17 +3894,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4473,17 +4473,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7575,17 +7575,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8515,17 +8515,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8745,17 +8745,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10276,17 +10276,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10514,17 +10514,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -11061,7 +11061,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11458,17 +11458,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -11744,24 +11744,24 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -12083,32 +12083,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12116,7 +12120,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12140,17 +12144,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12160,17 +12164,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12235,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12285,7 +12289,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -12313,32 +12317,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -12346,7 +12354,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12370,17 +12378,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12390,17 +12398,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -12428,32 +12436,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -12461,7 +12473,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12485,17 +12497,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12505,17 +12517,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -12576,7 +12588,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12625,12 +12637,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12703,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12735,17 +12747,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -12806,7 +12818,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12850,17 +12862,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>100.2</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-浦东78路.xlsx
+++ b/data/export/2026-09-30-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,17 +3537,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10157,17 +10157,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -11115,7 +11115,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11815,17 +11815,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -12120,7 +12120,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -12473,7 +12473,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12555,32 +12555,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12588,7 +12592,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12612,17 +12616,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12632,17 +12636,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -12703,7 +12707,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12818,7 +12822,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12872,7 +12876,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
